--- a/8 семестр/МиСИИ/ЛР Prolog 3/Экспертная система/грустная ферма.xlsx
+++ b/8 семестр/МиСИИ/ЛР Prolog 3/Экспертная система/грустная ферма.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosta\Documents\Учёба\8 семестр\МиСИИ\ЛР Prolog 3\Экспертная система\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E11CB12-336C-46BE-91D1-56B93CA975C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A54C1E-BE07-4998-9B68-A9B6337CA9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,22 +181,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -491,55 +487,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11"/>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1"/>
@@ -548,127 +537,109 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="D6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="B9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="10"/>
+      <c r="E10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
+      <c r="A12" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
